--- a/data/trans_dic/P22$notiene-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P22$notiene-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tiene Seguro Sanitario</t>
+          <t>Población que no tiene seguro médico (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,05</t>
+          <t>0,1; 1,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,42</t>
+          <t>0,0; 0,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,47</t>
+          <t>0,0; 0,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,56</t>
+          <t>0,07; 0,55</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,3</t>
+          <t>0,0; 0,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,57</t>
+          <t>0,06; 0,52</t>
         </is>
       </c>
     </row>
@@ -862,57 +862,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,38</t>
+          <t>0,0; 0,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,6</t>
+          <t>0,05; 0,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,27</t>
+          <t>0,0; 0,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 0,44</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,41</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,04; 0,42</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0,09; 0,5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,3</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,41</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,04; 0,45</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 0,48</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,28</t>
-        </is>
-      </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,23</t>
+          <t>0,0; 0,26</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,39</t>
+          <t>0,08; 0,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,27</t>
+          <t>0,05; 0,25</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,11</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1137,27 +1137,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,46</t>
+          <t>0,05; 0,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,33</t>
+          <t>0,04; 0,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,47</t>
+          <t>0,07; 0,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,21</t>
+          <t>0,03; 0,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,22</t>
+          <t>0,0; 0,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1167,17 +1167,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,24</t>
+          <t>0,02; 0,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,3</t>
+          <t>0,08; 0,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,26</t>
+          <t>0,05; 0,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,3</t>
+          <t>0,07; 0,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tiene Seguro Sanitario</t>
+          <t>Población que no tiene seguro médico (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1037; 10786</t>
+          <t>1036; 13000</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 8222</t>
+          <t>0; 7591</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1898</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5968</t>
+          <t>0; 5819</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5457</t>
+          <t>0; 5601</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2059</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2138</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3561</t>
+          <t>0; 3906</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1651; 13049</t>
+          <t>1652; 12910</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 6911</t>
+          <t>0; 10668</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 2029</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>837; 7213</t>
+          <t>808; 6573</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 8805</t>
+          <t>0; 8865</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 7401</t>
+          <t>0; 5255</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1054; 12527</t>
+          <t>1057; 13302</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6222</t>
+          <t>0; 5092</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4740</t>
+          <t>0; 6957</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 7217</t>
+          <t>0; 7182</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>843; 8881</t>
+          <t>844; 8320</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2221; 10700</t>
+          <t>2044; 11178</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 9169</t>
+          <t>0; 9849</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 8478</t>
+          <t>0; 9692</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2614; 15888</t>
+          <t>3132; 16489</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2472; 12382</t>
+          <t>2411; 11283</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2005</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6127</t>
+          <t>0; 6936</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 8506</t>
+          <t>0; 7677</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1821</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2019</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2132</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2001</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 1262</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2014</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 6554</t>
+          <t>0; 6027</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 7347</t>
+          <t>0; 8779</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 1489</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1652; 14932</t>
+          <t>1659; 15454</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1211; 11256</t>
+          <t>1211; 9940</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2280; 16005</t>
+          <t>2276; 15623</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>824; 7392</t>
+          <t>883; 7746</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 7585</t>
+          <t>0; 6450</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6073</t>
+          <t>0; 5999</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>851; 8465</t>
+          <t>849; 9300</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2810; 10958</t>
+          <t>2963; 11773</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3377; 17536</t>
+          <t>3139; 16800</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1268; 12887</t>
+          <t>1266; 12300</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4391; 20370</t>
+          <t>4538; 18934</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4720; 15424</t>
+          <t>4716; 15514</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$notiene-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P22$notiene-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,26</t>
+          <t>0,1; 1,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,43</t>
+          <t>0,0; 0,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -752,17 +752,17 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,52</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,55</t>
+          <t>0,07; 0,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,46</t>
+          <t>0,0; 0,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,52</t>
+          <t>0,07; 0,58</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,52</t>
+          <t>0,0; 0,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,27</t>
+          <t>0,0; 0,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,64</t>
+          <t>0,05; 0,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,22</t>
+          <t>0,0; 0,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,44</t>
+          <t>0,0; 0,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,41</t>
+          <t>0,0; 0,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,42</t>
+          <t>0,04; 0,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,5</t>
+          <t>0,11; 0,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,3</t>
+          <t>0,0; 0,28</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,26</t>
+          <t>0,0; 0,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,41</t>
+          <t>0,07; 0,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,25</t>
+          <t>0,09; 0,38</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,44</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,27 +1104,27 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>0,16%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,47</t>
+          <t>0,05; 0,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1147,37 +1147,37 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,46</t>
+          <t>0,07; 0,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,22</t>
+          <t>0,03; 0,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,19</t>
+          <t>0,0; 0,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,17</t>
+          <t>0,0; 0,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,26</t>
+          <t>0,02; 0,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,32</t>
+          <t>0,07; 0,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,25</t>
+          <t>0,04; 0,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,27</t>
+          <t>0,06; 0,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,22</t>
+          <t>0,09; 0,27</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>3256</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1036; 13000</t>
+          <t>1033; 12542</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 7591</t>
+          <t>0; 6846</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1519,12 +1519,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5819</t>
+          <t>0; 7628</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5601</t>
+          <t>0; 4647</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1539,17 +1539,17 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3906</t>
+          <t>0; 4645</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1652; 12910</t>
+          <t>1645; 13703</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 10668</t>
+          <t>0; 6940</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>808; 6573</t>
+          <t>914; 8106</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>8321</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 8865</t>
+          <t>0; 11581</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5255</t>
+          <t>0; 4979</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1057; 13302</t>
+          <t>1056; 15665</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5092</t>
+          <t>0; 10776</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6957</t>
+          <t>0; 4960</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 7182</t>
+          <t>0; 6740</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>844; 8320</t>
+          <t>851; 8908</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2044; 11178</t>
+          <t>2289; 10806</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 9849</t>
+          <t>0; 9168</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 9692</t>
+          <t>0; 8552</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3132; 16489</t>
+          <t>2909; 16948</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2411; 11283</t>
+          <t>4099; 16899</t>
         </is>
       </c>
     </row>
@@ -1925,12 +1925,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6936</t>
+          <t>0; 6088</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7677</t>
+          <t>0; 8592</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 6027</t>
+          <t>0; 4876</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 8779</t>
+          <t>0; 7424</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5995</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8863</t>
+          <t>11577</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1659; 15454</t>
+          <t>1656; 15998</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1211; 9940</t>
+          <t>1204; 9947</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2276; 15623</t>
+          <t>2446; 16165</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>883; 7746</t>
+          <t>1147; 12570</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6450</t>
+          <t>0; 7014</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5999</t>
+          <t>0; 5186</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>849; 9300</t>
+          <t>846; 8731</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2963; 11773</t>
+          <t>2792; 11977</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3139; 16800</t>
+          <t>2864; 17250</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1266; 12300</t>
+          <t>1232; 12613</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4538; 18934</t>
+          <t>4221; 19012</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4716; 15514</t>
+          <t>6424; 19729</t>
         </is>
       </c>
     </row>
